--- a/data/s3/Aradas/archetypes/v2g_behaviour.xlsx
+++ b/data/s3/Aradas/archetypes/v2g_behaviour.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Aradas\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFF1F56-FB94-4184-BA46-074BE3ABA9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18117E03-6DB2-4A93-9AB1-A5FA7425FC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plug-in choices" sheetId="3" r:id="rId1"/>
@@ -71,15 +71,9 @@
     <t>B_INCOME_HIGH</t>
   </si>
   <si>
-    <t>The influence of high income (household monthly income &gt;=6000 euros)</t>
-  </si>
-  <si>
     <t>B_INCOME_LOW</t>
   </si>
   <si>
-    <t>The influence of low income (household monthly income &lt;3000 euros)</t>
-  </si>
-  <si>
     <t>B_LOCATION_SHOPPING</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
     <t xml:space="preserve">B_WAIT_TIME </t>
   </si>
   <si>
-    <t>The influence of the waiting time for an available charger</t>
-  </si>
-  <si>
     <t>B_WALK_TIME</t>
   </si>
   <si>
@@ -318,6 +309,15 @@
   </si>
   <si>
     <t>Sensitivity to travel time for V2G alternatives if the current travel mode is public transport or bike.</t>
+  </si>
+  <si>
+    <t>The influence of high income (household monthly income &gt;3000 euros)</t>
+  </si>
+  <si>
+    <t>The influence of low income (household monthly income &lt;=1500 euros)</t>
+  </si>
+  <si>
+    <t>The influence of the waiting time to go to a charging station</t>
   </si>
 </sst>
 </file>
@@ -661,13 +661,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -678,7 +678,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>1.194876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -689,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>-1.0678E-2</v>
+        <v>6.4000000000000003E-3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -700,7 +700,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>2.1250000000000002E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -711,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>0.114299</v>
+        <v>0.27550000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -733,7 +733,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1.1369000000000001E-2</v>
+        <v>4.7999999999999996E-3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -741,87 +741,87 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.7722</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.32879999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.47439999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.54190000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12">
-        <v>7.4088000000000001E-2</v>
+        <v>0.14080000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>-1.128E-2</v>
+        <v>-3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>-7.8799999999999995E-2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>-4.802E-2</v>
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -844,30 +844,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>-2.7322000000000002</v>
@@ -884,52 +884,52 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C6">
         <v>-2.7812000000000001</v>
@@ -946,24 +946,24 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>0.91559999999999997</v>
@@ -980,10 +980,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>-2.3037999999999998</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>-3.0099999999999998E-2</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>-1.3299999999999999E-2</v>
@@ -1040,24 +1040,24 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>-5.62E-2</v>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>-0.32329999999999998</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15">
         <v>0.92210000000000003</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C16">
         <v>-0.53029999999999999</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>-0.1885</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>1.1519999999999999</v>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C19">
         <v>0.2457</v>
@@ -1194,24 +1194,24 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>0.1794</v>
@@ -1228,66 +1228,66 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C26">
         <v>-0.27789999999999998</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C27">
         <v>-8.3999999999999995E-3</v>
@@ -1342,30 +1342,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>-5.9951999999999996</v>
@@ -1382,24 +1382,24 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1411,15 +1411,15 @@
         <v>1.48</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>-1.2944</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>-3.95E-2</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1471,15 +1471,15 @@
         <v>0.31</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>-0.1792</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>-0.29870000000000002</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10">
         <v>1.0047999999999999</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>-0.71109999999999995</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12">
         <v>-0.40300000000000002</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13">
         <v>1.119</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>0.2349</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>0.68189999999999995</v>
@@ -1636,52 +1636,52 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>-0.4264</v>
@@ -1692,16 +1692,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/s3/Aradas/archetypes/v2g_behaviour.xlsx
+++ b/data/s3/Aradas/archetypes/v2g_behaviour.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18117E03-6DB2-4A93-9AB1-A5FA7425FC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7C92A5-EB27-41F5-A31B-B16B54A6B90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plug-in choices" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
   <si>
     <t xml:space="preserve">Description </t>
   </si>
@@ -176,12 +176,6 @@
     <t>Alternative specific constant for private EV with V2G (EV2G) if the respondent’s current travel mode is public transport.</t>
   </si>
   <si>
-    <t>B_AGE_CSV2G</t>
-  </si>
-  <si>
-    <t>Effect of age (continuous) on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
     <t>B_AGE_EV2G</t>
   </si>
   <si>
@@ -200,36 +194,12 @@
     <t>Cost sensitivity applicable to all alternatives and all users.</t>
   </si>
   <si>
-    <t>B_EDUCATION_CSV2G</t>
-  </si>
-  <si>
-    <t>Effect of education level on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
     <t>B_EV_OWNERSHIP_CSV2G</t>
   </si>
   <si>
-    <t>Effect of EV ownership on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
-    <t>B_GENDER_CSV2G</t>
-  </si>
-  <si>
-    <t>Effect of gender (being women) on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
     <t>B_HAVING_KIDS_CSV2G</t>
   </si>
   <si>
-    <t>Effect of having children on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
-    <t>B_INCOME_HIGH_CSV2G</t>
-  </si>
-  <si>
-    <t>Effect of high household income on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
     <t>B_INCOME_LOW_CSV2G</t>
   </si>
   <si>
@@ -290,24 +260,9 @@
     <t>Effect of owning a private EV (EV owner = 1) on choosing carsharing with V2G (CSV2G), relative to non-EV owners.</t>
   </si>
   <si>
-    <t>Effect of being female (female = 1, relative to male) on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
     <t>Effect of having children (yes = 1) on choosing carsharing with V2G (CSV2G).</t>
   </si>
   <si>
-    <t>Effect of high household income (income &gt; €3000) on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
-    <t>Effect of low household income (income&lt;=1500)on choosing carsharing with V2G (CSV2G).</t>
-  </si>
-  <si>
-    <t>B_Time_PTBike</t>
-  </si>
-  <si>
-    <t>B_Time_V2G_PTBikeUser</t>
-  </si>
-  <si>
     <t>Sensitivity to travel time for V2G alternatives if the current travel mode is public transport or bike.</t>
   </si>
   <si>
@@ -318,6 +273,18 @@
   </si>
   <si>
     <t>The influence of the waiting time to go to a charging station</t>
+  </si>
+  <si>
+    <t>B_EV_OWNERSHIP_EV2G</t>
+  </si>
+  <si>
+    <t>Effect of owning a private EV (EV owner = 1) on choosing private EV with V2G (EV2G), relative to non-EV owners.</t>
+  </si>
+  <si>
+    <t>B_HAVING_KIDS_V2G</t>
+  </si>
+  <si>
+    <t>Effect of having children (yes = 1) on choosing both V2G alternatives (CSV2G and EV2G).</t>
   </si>
 </sst>
 </file>
@@ -367,11 +334,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,13 +628,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -741,7 +709,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>0.7722</v>
@@ -752,7 +720,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>0.32879999999999998</v>
@@ -807,7 +775,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>-7.8799999999999995E-2</v>
@@ -843,484 +811,500 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C2">
-        <v>-2.7322000000000002</v>
-      </c>
-      <c r="D2">
-        <v>0.66379999999999995</v>
-      </c>
-      <c r="E2">
-        <v>-4.1159999999999997</v>
-      </c>
-      <c r="F2">
+      <c r="C2" s="4">
+        <v>-3.6230000000000002</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.156</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-23.169</v>
+      </c>
+      <c r="F2" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C3" s="4">
+        <v>-1.7450000000000001</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-10.458</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-1.6619999999999999</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-12.32</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-1.119</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.219</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="4">
+        <v>-2.895</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="E6" s="4">
+        <v>-17.152999999999999</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4">
+        <v>-0.57399999999999995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="E7" s="4">
+        <v>-3.1680000000000001</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="4">
+        <v>-0.53900000000000003</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="E8" s="4">
+        <v>-3.6869999999999998</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="4">
+        <v>-0.60499999999999998</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.224</v>
+      </c>
+      <c r="E9" s="4">
+        <v>-2.6970000000000001</v>
+      </c>
+      <c r="F9" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2E-3</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2.5750000000000002</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="4">
+        <v>-5.1999999999999998E-2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="4">
+        <v>-5.0030000000000001</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="D13" s="4">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>5.1559999999999997</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9.6310000000000002</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="4">
+        <v>-0.27700000000000002</v>
+      </c>
+      <c r="D15" s="4">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>-3.6059999999999999</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="D16" s="4">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>5.1180000000000003</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="4">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="E17" s="4">
+        <v>-2.2919999999999998</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6">
-        <v>-2.7812000000000001</v>
-      </c>
-      <c r="D6">
-        <v>0.65610000000000002</v>
-      </c>
-      <c r="E6">
-        <v>-4.2390999999999996</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8">
-        <v>0.91559999999999997</v>
-      </c>
-      <c r="D8">
-        <v>0.29980000000000001</v>
-      </c>
-      <c r="E8">
-        <v>3.0541999999999998</v>
-      </c>
-      <c r="F8">
-        <v>2.3E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9">
-        <v>-2.3037999999999998</v>
-      </c>
-      <c r="D9">
-        <v>0.44180000000000003</v>
-      </c>
-      <c r="E9">
-        <v>-5.2145999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10">
-        <v>-3.0099999999999998E-2</v>
-      </c>
-      <c r="D10">
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="E10">
-        <v>-10.2341</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11">
-        <v>-1.3299999999999999E-2</v>
-      </c>
-      <c r="D11">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="E11">
-        <v>-5.4028</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13">
-        <v>-5.62E-2</v>
-      </c>
-      <c r="D13">
-        <v>1.9699999999999999E-2</v>
-      </c>
-      <c r="E13">
-        <v>-2.8523000000000001</v>
-      </c>
-      <c r="F13">
-        <v>4.3E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14">
-        <v>-0.32329999999999998</v>
-      </c>
-      <c r="D14">
-        <v>0.10059999999999999</v>
-      </c>
-      <c r="E14">
-        <v>-3.2143999999999999</v>
-      </c>
-      <c r="F14">
-        <v>1.2999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15">
-        <v>0.92210000000000003</v>
-      </c>
-      <c r="D15">
-        <v>0.1678</v>
-      </c>
-      <c r="E15">
-        <v>5.4950999999999999</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16">
-        <v>-0.53029999999999999</v>
-      </c>
-      <c r="D16">
-        <v>8.0600000000000005E-2</v>
-      </c>
-      <c r="E16">
-        <v>-6.5797999999999996</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C17">
-        <v>-0.1885</v>
-      </c>
-      <c r="D17">
-        <v>9.8799999999999999E-2</v>
-      </c>
-      <c r="E17">
-        <v>-1.9088000000000001</v>
-      </c>
-      <c r="F17">
-        <v>5.6300000000000003E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="C19" s="4">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E19" s="4">
+        <v>-2.0619999999999998</v>
+      </c>
+      <c r="F19" s="4">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C18">
-        <v>1.1519999999999999</v>
-      </c>
-      <c r="D18">
-        <v>0.18190000000000001</v>
-      </c>
-      <c r="E18">
-        <v>6.3334000000000001</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C20" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2E-3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3.5489999999999999</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C19">
-        <v>0.2457</v>
-      </c>
-      <c r="D19">
-        <v>8.5599999999999996E-2</v>
-      </c>
-      <c r="E19">
-        <v>2.8706</v>
-      </c>
-      <c r="F19">
-        <v>4.1000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="C21" s="4">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-5.319</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="C22" s="4">
+        <v>-5.5E-2</v>
+      </c>
+      <c r="D22" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>-12.738</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C21">
-        <v>0.1794</v>
-      </c>
-      <c r="D21">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E21">
-        <v>3.1204000000000001</v>
-      </c>
-      <c r="F21">
-        <v>1.8E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="C23" s="4">
+        <v>-0.151</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>-6.9630000000000001</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>36</v>
+      <c r="C24" s="4">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E24" s="4">
+        <v>-10.747999999999999</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26">
-        <v>-0.27789999999999998</v>
-      </c>
-      <c r="D26">
-        <v>3.8100000000000002E-2</v>
-      </c>
-      <c r="E26">
-        <v>-7.3003999999999998</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27">
-        <v>-8.3999999999999995E-3</v>
-      </c>
-      <c r="D27">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="E27">
-        <v>-1.7804</v>
-      </c>
-      <c r="F27">
-        <v>7.4999999999999997E-2</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1330,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABED8AC-90DF-4C58-A1F5-329F3BE9A773}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
@@ -1368,13 +1352,13 @@
         <v>33</v>
       </c>
       <c r="C2">
-        <v>-5.9951999999999996</v>
+        <v>-3.3290000000000002</v>
       </c>
       <c r="D2">
-        <v>0.34129999999999999</v>
+        <v>0.222</v>
       </c>
       <c r="E2">
-        <v>-17.567399999999999</v>
+        <v>-15.015000000000001</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1388,10 +1372,16 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
+        <v>-1.871</v>
+      </c>
+      <c r="D3">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="E3">
+        <v>-8.2040000000000006</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1402,16 +1392,16 @@
         <v>38</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>-1.383</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="E4">
-        <v>1.48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
+        <v>-8.4290000000000003</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1422,36 +1412,30 @@
         <v>40</v>
       </c>
       <c r="C5">
-        <v>-1.2944</v>
+        <v>-0.97399999999999998</v>
       </c>
       <c r="D5">
-        <v>0.55910000000000004</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="E5">
-        <v>-2.3153999999999999</v>
+        <v>-3.6869999999999998</v>
       </c>
       <c r="F5">
-        <v>2.06E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>-3.95E-2</v>
-      </c>
-      <c r="D6">
-        <v>3.8E-3</v>
-      </c>
-      <c r="E6">
-        <v>-10.3848</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1459,19 +1443,19 @@
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>-2.5999999999999999E-2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="E7">
-        <v>0.31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
+        <v>-2.1240000000000001</v>
+      </c>
+      <c r="F7">
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1479,16 +1463,16 @@
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>-0.1792</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="D8">
-        <v>3.5200000000000002E-2</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="E8">
-        <v>-5.0937999999999999</v>
+        <v>5.7869999999999999</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1496,99 +1480,93 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>-0.29870000000000002</v>
-      </c>
-      <c r="D9">
-        <v>0.1235</v>
-      </c>
-      <c r="E9">
-        <v>-2.4180000000000001</v>
-      </c>
-      <c r="F9">
-        <v>1.5599999999999999E-2</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>1.0047999999999999</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="D10">
-        <v>0.2094</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="E10">
-        <v>4.7981999999999996</v>
+        <v>3.4129999999999998</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="C11">
-        <v>-0.71109999999999995</v>
+        <v>-3.1E-2</v>
       </c>
       <c r="D11">
-        <v>0.1021</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E11">
-        <v>-6.9657999999999998</v>
+        <v>-2.0590000000000002</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3.9E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C12">
-        <v>-0.40300000000000002</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D12">
-        <v>0.12509999999999999</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E12">
-        <v>-3.2208000000000001</v>
+        <v>2.7440000000000002</v>
       </c>
       <c r="F12">
-        <v>1.2999999999999999E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C13">
-        <v>1.119</v>
+        <v>-2.5999999999999999E-2</v>
       </c>
       <c r="D13">
-        <v>0.219</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E13">
-        <v>5.1085000000000003</v>
+        <v>-4.6360000000000001</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1596,112 +1574,62 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C14">
-        <v>0.2349</v>
+        <v>-5.1999999999999998E-2</v>
       </c>
       <c r="D14">
-        <v>0.108</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E14">
-        <v>2.1753</v>
+        <v>-10.468</v>
       </c>
       <c r="F14">
-        <v>2.9600000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15">
-        <v>0.68189999999999995</v>
+        <v>-0.13400000000000001</v>
       </c>
       <c r="D15">
-        <v>0.26440000000000002</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E15">
-        <v>2.5792000000000002</v>
+        <v>-5.5010000000000003</v>
       </c>
       <c r="F15">
-        <v>9.9000000000000008E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19">
-        <v>-0.4264</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="D16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E16">
+        <v>-5.4980000000000002</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
